--- a/hexameters/corpus.xlsx
+++ b/hexameters/corpus.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinapaccara/Documents/Documenti/Università/POST-LAUREA/DOTTORATO/Lavoro/Digitale/Stilometria/Esametri/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinapaccara/Documents/Documenti/Università/POST-LAUREA/DOTTORATO/Lavoro/Digitale/Stilometria/hexameters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E75E9DC-45BB-1B42-8B6B-F112BCA956A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003F49BD-9F08-1940-AC01-41C4E8877D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5860" yWindow="620" windowWidth="22940" windowHeight="15100" xr2:uid="{0A81A14F-60F6-FB4D-8AF2-4DB4EE2AB397}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="133">
   <si>
     <t>Hildebertus Cenomanensis</t>
   </si>
@@ -429,6 +429,12 @@
   </si>
   <si>
     <t>Liber decem capitulorum</t>
+  </si>
+  <si>
+    <t>H_epigrammata</t>
+  </si>
+  <si>
+    <t>Epigrammata biblica</t>
   </si>
 </sst>
 </file>
@@ -957,7 +963,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{316805FE-F53C-1342-A640-F5413BD5C191}">
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.6640625" style="12" bestFit="1" customWidth="1"/>
@@ -1309,113 +1315,114 @@
       </c>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="1:11" s="2" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D18" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="12">
+        <v>2645</v>
+      </c>
+      <c r="F18" s="12">
+        <v>394</v>
+      </c>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:11" s="2" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E19" s="7">
         <v>5836</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F19" s="12">
         <v>849</v>
       </c>
-      <c r="H18"/>
-    </row>
-    <row r="19" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E19" s="7">
-        <v>15002</v>
-      </c>
-      <c r="F19" s="12">
-        <v>2200</v>
-      </c>
+      <c r="H19"/>
     </row>
     <row r="20" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>76</v>
       </c>
       <c r="E20" s="7">
-        <v>21710</v>
+        <v>15002</v>
       </c>
       <c r="F20" s="12">
-        <v>3424</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="7">
+        <v>21710</v>
+      </c>
+      <c r="F21" s="12">
+        <v>3424</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B22" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C22" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="7">
+      <c r="D22" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="7">
         <v>26553</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F22" s="12">
         <v>4270</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" s="7">
-        <v>8513</v>
-      </c>
-      <c r="F22" s="12">
-        <v>1292</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>125</v>
@@ -1424,202 +1431,202 @@
         <v>76</v>
       </c>
       <c r="E23" s="7">
+        <v>8513</v>
+      </c>
+      <c r="F23" s="12">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" s="7">
         <v>3469</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F24" s="12">
         <v>470</v>
       </c>
     </row>
-    <row r="24" spans="1:11" s="18" customFormat="1" ht="14" x14ac:dyDescent="0.2">
-      <c r="A24" s="12" t="s">
+    <row r="25" spans="1:11" s="18" customFormat="1" ht="14" x14ac:dyDescent="0.2">
+      <c r="A25" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B25" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C25" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="D24" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E24" s="12">
+      <c r="D25" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25" s="12">
         <v>4105</v>
       </c>
-      <c r="F24" s="18">
+      <c r="F25" s="18">
         <v>632</v>
       </c>
     </row>
-    <row r="25" spans="1:11" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+    <row r="26" spans="1:11" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B26" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C26" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E25" s="7">
+      <c r="D26" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" s="7">
         <v>23115</v>
       </c>
-      <c r="F25" s="12">
+      <c r="F26" s="12">
         <v>3597</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E26" s="7">
-        <v>15647</v>
-      </c>
-      <c r="F26" s="12">
-        <v>2302</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>76</v>
       </c>
       <c r="E27" s="7">
-        <v>22466</v>
+        <v>15647</v>
       </c>
       <c r="F27" s="12">
-        <v>3486</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>76</v>
       </c>
       <c r="E28" s="7">
-        <v>11523</v>
+        <v>22466</v>
       </c>
       <c r="F28" s="12">
-        <v>1725</v>
-      </c>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
+        <v>3486</v>
+      </c>
     </row>
     <row r="29" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>76</v>
       </c>
       <c r="E29" s="7">
-        <v>6489</v>
+        <v>11523</v>
       </c>
       <c r="F29" s="12">
-        <v>939</v>
-      </c>
+        <v>1725</v>
+      </c>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
     </row>
     <row r="30" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>76</v>
       </c>
       <c r="E30" s="7">
-        <v>5521</v>
+        <v>6489</v>
       </c>
       <c r="F30" s="12">
-        <v>867</v>
+        <v>939</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E31" s="7">
-        <v>2135</v>
+        <v>5521</v>
       </c>
       <c r="F31" s="12">
-        <v>298</v>
+        <v>867</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>73</v>
       </c>
       <c r="E32" s="7">
-        <v>2130</v>
+        <v>2135</v>
       </c>
       <c r="F32" s="12">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>11</v>
@@ -1628,18 +1635,18 @@
         <v>73</v>
       </c>
       <c r="E33" s="7">
-        <v>2729</v>
+        <v>2130</v>
       </c>
       <c r="F33" s="12">
-        <v>418</v>
+        <v>305</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
-        <v>93</v>
+      <c r="A34" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>11</v>
@@ -1647,39 +1654,39 @@
       <c r="D34" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E34" s="13">
-        <v>9513</v>
-      </c>
-      <c r="F34" s="18">
-        <v>1518</v>
+      <c r="E34" s="7">
+        <v>2729</v>
+      </c>
+      <c r="F34" s="12">
+        <v>418</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>94</v>
+      <c r="A35" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E35" s="7">
-        <v>44017</v>
-      </c>
-      <c r="F35" s="12">
-        <v>6560</v>
+        <v>73</v>
+      </c>
+      <c r="E35" s="13">
+        <v>9513</v>
+      </c>
+      <c r="F35" s="18">
+        <v>1518</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>11</v>
@@ -1688,18 +1695,18 @@
         <v>76</v>
       </c>
       <c r="E36" s="7">
-        <v>30735</v>
+        <v>44017</v>
       </c>
       <c r="F36" s="12">
-        <v>4769</v>
+        <v>6560</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>11</v>
@@ -1708,18 +1715,18 @@
         <v>76</v>
       </c>
       <c r="E37" s="7">
-        <v>4116</v>
+        <v>30735</v>
       </c>
       <c r="F37" s="12">
-        <v>355</v>
+        <v>4769</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>11</v>
@@ -1728,18 +1735,18 @@
         <v>76</v>
       </c>
       <c r="E38" s="7">
-        <v>14482</v>
+        <v>4116</v>
       </c>
       <c r="F38" s="12">
-        <v>2091</v>
+        <v>355</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>11</v>
@@ -1748,18 +1755,18 @@
         <v>76</v>
       </c>
       <c r="E39" s="7">
-        <v>13179</v>
-      </c>
-      <c r="F39" s="17">
-        <v>1736</v>
+        <v>14482</v>
+      </c>
+      <c r="F39" s="12">
+        <v>2091</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>11</v>
@@ -1768,58 +1775,58 @@
         <v>76</v>
       </c>
       <c r="E40" s="7">
+        <v>13179</v>
+      </c>
+      <c r="F40" s="17">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E41" s="7">
         <v>20718</v>
       </c>
-      <c r="F40" s="12">
+      <c r="F41" s="12">
         <v>1493</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="15" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B42" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C42" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D41" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E41" s="16">
+      <c r="D42" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E42" s="16">
         <v>15468</v>
       </c>
-      <c r="F41" s="12">
+      <c r="F42" s="12">
         <v>2287</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E42" s="7">
-        <v>12353</v>
-      </c>
-      <c r="F42" s="12">
-        <v>1925</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>11</v>
@@ -1828,58 +1835,58 @@
         <v>76</v>
       </c>
       <c r="E43" s="7">
+        <v>12353</v>
+      </c>
+      <c r="F43" s="12">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E44" s="7">
         <v>22284</v>
       </c>
-      <c r="F43" s="12">
+      <c r="F44" s="12">
         <v>3338</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12">
-        <f>SUM(E20:E41)</f>
-        <v>308333</v>
-      </c>
-      <c r="F44" s="12">
-        <f>SUM(F2:F43)</f>
-        <v>101439</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="1"/>
+      <c r="E45" s="12">
+        <f>SUM(E2:E44)</f>
+        <v>713653</v>
+      </c>
+      <c r="F45" s="12">
+        <f>SUM(F2:F44)</f>
+        <v>101833</v>
+      </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="E46" s="12">
-        <v>3655</v>
-      </c>
-      <c r="F46" s="12">
-        <v>564</v>
-      </c>
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="1"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C47" s="12" t="s">
         <v>11</v>
@@ -1888,18 +1895,18 @@
         <v>112</v>
       </c>
       <c r="E47" s="12">
-        <v>1002</v>
+        <v>3655</v>
       </c>
       <c r="F47" s="12">
-        <v>157</v>
+        <v>564</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C48" s="12" t="s">
         <v>11</v>
@@ -1908,18 +1915,18 @@
         <v>112</v>
       </c>
       <c r="E48" s="12">
-        <v>3085</v>
+        <v>1002</v>
       </c>
       <c r="F48" s="12">
-        <v>478</v>
+        <v>157</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>11</v>
@@ -1928,21 +1935,41 @@
         <v>112</v>
       </c>
       <c r="E49" s="12">
+        <v>3085</v>
+      </c>
+      <c r="F49" s="12">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="E50" s="12">
         <v>958</v>
       </c>
-      <c r="F49" s="18">
+      <c r="F50" s="18">
         <v>151</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B51" s="12"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F43">
-    <sortCondition ref="A2:A43"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F44">
+    <sortCondition ref="A2:A44"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
